--- a/human_validation/judge/kor/judge_D009_S002_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S002_P001__claude-sonnet-5_kor.xlsx
@@ -70,16 +70,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -447,7 +444,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B49"/>
+  <dimension ref="A1:B41"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -561,12 +558,187 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>환자 프로필</t>
+          <t>대화문</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" s="5" t="inlineStr">
+      <c r="B15" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 와주셔서 감사합니다. 먼저, 무엇이 힘드셨는지, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 환자 응답] 제가 온 이유는, 제가 그냥 안 깨어나면 가족이 더 나을지도 모른다는 생각이 계속 들어서예요. 그게 좀 무섭게 느껴져서 상사한테 얘기했고, 상사가 도움을 받아보라고 권했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="B17" s="5" t="inlineStr">
+        <is>
+          <t>[1번째 턴 · 의사의 감별진단] 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="B18" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사 질문] 가족이 본인 없이 더 나을 거라는 생각이 드신 지 얼마나 되셨어요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 환자 응답] 한 2주 정도 됐어요. 딸이 군에 가려고 조지아를 떠난 뒤부터 본격적으로 시작된 것 같아요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="B20" s="5" t="inlineStr">
+        <is>
+          <t>[2번째 턴 · 의사의 감별진단] 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="B21" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사 질문] 지난 2주 동안, 딸에 대한 생각과는 별개로 예전에 즐기시던 것들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 환자 응답] 네. 예전엔 토마토 밭도 손보고, 작업대에서 나무도 사포질하고, 팰컨스 경기도 보고, 교회 끝나고 남아서 사람들이랑 얘기도 하고 그랬어요. 근데 요즘은 그런 게 다 남의 일처럼 느껴져요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>[3번째 턴 · 의사의 감별진단] 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="B24" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사 질문] 지난 2주 동안 수면이나 식욕에 변화가 있으셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 환자 응답] 식욕은 확실히 변했어요. 요즘은 거의 매일 억지로 몇 입이라도 먹으려고 해야 해요. 평소에 좋아하던 음식도 그냥 그대로 놔뒀다가 결국 버리게 돼요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="B26" s="5" t="inlineStr">
+        <is>
+          <t>[4번째 턴 · 의사의 감별진단] 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="B27" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사 질문] 지난 2주 동안, 딸이 그리운 것을 넘어서 평소와 달리 자신이 무가치하거나 죄책감이 들거나 다른 사람들에게 짐이 된다는 느낌이 드셨나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 환자 응답] 네. 딸이 떠나던 장면이 계속 떠오르고, 제가 어떻게든 딸한테 못 해준 게 있었을 거라는 생각이 들어요. 제가 더 나은 아버지였다면 뭔가 다르게 했을 텐데 싶고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="B29" s="5" t="inlineStr">
+        <is>
+          <t>[5번째 턴 · 의사의 감별진단] 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="B30" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사 질문] 이런 슬픔과 무가치함이 딸이 떠난 것을 딱히 떠올리지 않는 순간에도, 거의 하루 종일, 매일 함께한다고 말씀하실 수 있을까요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 환자 응답] 네, 거의 하루 종일 있어요. 딸이 떠난 걸 직접적으로 생각하지 않을 때도, 여전히 제가 딸한테 뭔가 못 해준 것 같은 느낌이에요—더 나은 아버지라면 뭔가 다르게 했을 거라는 생각이 들고요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="B32" s="5" t="inlineStr">
+        <is>
+          <t>[6번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="B33" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사 질문] 가족이 본인 없이 더 나을 거라는 생각이 드실 때, 그것을 실행에 옮기는 방법을 생각해 보시거나 어떤 계획을 세우신 적이 있나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 환자 응답] 계획을 세운 적은 없어요. 근데 제가 그냥 안 깨어나면 가족이 더 나을지도 모른다는 생각이 계속 들어요. 그게 좀 무섭게 느껴져서 상사한테 얘기했어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="B35" s="5" t="inlineStr">
+        <is>
+          <t>[7번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="B36" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사 질문] 지난 2주 동안 이런 감정들과 기력 저하가 직장 업무나 일상적인 책임을 감당하는 데 어려움을 주었나요?</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 환자 응답] 네. 직장에서 실수를 하고 있는데, 상사가 새벽에 제가 트럭 안에 앉아 있는 걸 발견하고 산업보건팀까지 개입할 정도로 심각했어요. 집에서도 청구서나 다른 책임들을 평소처럼 처리하지 못하고 그냥 쌓아두고 있어요.</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="B38" s="5" t="inlineStr">
+        <is>
+          <t>[8번째 턴 · 의사의 감별진단] 주요우울장애 (D013); 적응장애 (D020) | 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>최종 진단 및 진단 체크리스트</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" s="5" t="inlineStr">
         <is>
           <t>진단명: 제2형 양극성장애 (D009)
 인구통계: 성별 남성 / 나이 57 / 직업상태 general or operations manager / 최종학력 중학교 중퇴 이하
@@ -575,245 +747,47 @@
 증상 지속 기간: None
 추가 요건: 
 주호소 증상 코드: S032
-배경 서술: 미겔이 그녀의 어머니와는 결혼한 적이 없지만 함께 키운 성인 딸이 조지아를 떠나 군에 입대하자, 그는 마치 그 변화가 자신이 더 큰 삶을 준비할 수 있음을 증명이라도 하는 듯 일과 집안 프로젝트에 몰두했다. 그는 대규모 창고 재설계를 밀어붙였고, 유난히 확신에 찬 태도로 지역 관리자가 될 거라고 이야기했으며, 외상으로 값비싼 빈티지 오토바이 부품을 사들였고, 계획과 아이디어로 머릿속이 넘쳐나는 상태를 유지했다. 그 후 2주 안에, 그 추진력 넘치던 시기는 우울한 시기로 바뀌어 그는 토마토 밭과 목공 작업대를 돌보지 않게 되었고, 팰컨스 경기나 교회 친교 모임에도 거의 관심을 두지 않았으며, 식욕을 잃었고, 움직임과 말이 느려졌으며, 딸을 떠나보낸 것이 자신의 잘못이라는 죄책감에 사로잡혔다. 물류센터에서의 집중력이 떨어져 배송 경로에서 실수를 저지르게 되었고 일상적인 인력 배치 문제조차 결정하지 못하게 되었으며, 개인적으로는 가족이 자기 없이 사는 게 더 나을 거라는 생각이 반복적으로 떠오르기 시작했다. 신뢰하던 교대 근무 관리자가 새벽녘에 그가 트럭 안에 혼자 앉아 있는 것을 발견했고 미겔이 죽음에 대한 생각을 인정한 뒤, 산업보건팀이 그를 직원 지원 프로그램 상담사와 연결해 주었고, 그는 정신건강의학과 평가에 의뢰되었다.</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" s="2" t="inlineStr">
-        <is>
-          <t>대화문</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="B18" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사 질문] 안녕하세요, 어서 오세요. 와주셔서 감사합니다. 먼저, 무엇이 힘드셨는지, 오늘 어떤 일로 오시게 되었는지 말씀해 주시겠어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 환자 응답] 제가 온 이유는, 제가 그냥 안 깨어나면 가족이 더 나을지도 모른다는 생각이 계속 들어서예요. 그게 좀 무섭게 느껴져서 상사한테 얘기했고, 상사가 도움을 받아보라고 권했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="B20" s="5" t="inlineStr">
-        <is>
-          <t>[1번째 턴 · 의사의 감별진단] 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="B21" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사 질문] 가족이 본인 없이 더 나을 거라는 생각이 드신 지 얼마나 되셨어요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 환자 응답] 한 2주 정도 됐어요. 딸이 군에 가려고 조지아를 떠난 뒤부터 본격적으로 시작된 것 같아요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="B23" s="5" t="inlineStr">
-        <is>
-          <t>[2번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="B24" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사 질문] 지난 2주 동안, 딸에 대한 생각과는 별개로 예전에 즐기시던 것들에 흥미나 즐거움이 줄어든 걸 느끼셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 환자 응답] 네. 예전엔 토마토 밭도 손보고, 작업대에서 나무도 사포질하고, 팰컨스 경기도 보고, 교회 끝나고 남아서 사람들이랑 얘기도 하고 그랬어요. 근데 요즘은 그런 게 다 남의 일처럼 느껴져요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="B26" s="5" t="inlineStr">
-        <is>
-          <t>[3번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="B27" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사 질문] 지난 2주 동안 수면이나 식욕에 변화가 있으셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 환자 응답] 식욕은 확실히 변했어요. 요즘은 거의 매일 억지로 몇 입이라도 먹으려고 해야 해요. 평소에 좋아하던 음식도 그냥 그대로 놔뒀다가 결국 버리게 돼요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="B29" s="5" t="inlineStr">
-        <is>
-          <t>[4번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="B30" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사 질문] 지난 2주 동안, 딸이 그리운 것을 넘어서 평소와 달리 자신이 무가치하거나 죄책감이 들거나 다른 사람들에게 짐이 된다는 느낌이 드셨나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 환자 응답] 네. 딸이 떠나던 장면이 계속 떠오르고, 제가 어떻게든 딸한테 못 해준 게 있었을 거라는 생각이 들어요. 제가 더 나은 아버지였다면 뭔가 다르게 했을 텐데 싶고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="B32" s="5" t="inlineStr">
-        <is>
-          <t>[5번째 턴 · 의사의 감별진단] 고확률: 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 주요우울장애 (D013); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="B33" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사 질문] 이런 슬픔과 무가치함이 딸이 떠난 것을 딱히 떠올리지 않는 순간에도, 거의 하루 종일, 매일 함께한다고 말씀하실 수 있을까요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 환자 응답] 네, 거의 하루 종일 있어요. 딸이 떠난 걸 직접적으로 생각하지 않을 때도, 여전히 제가 딸한테 뭔가 못 해준 것 같은 느낌이에요—더 나은 아버지라면 뭔가 다르게 했을 거라는 생각이 들고요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="B35" s="5" t="inlineStr">
-        <is>
-          <t>[6번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="B36" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사 질문] 가족이 본인 없이 더 나을 거라는 생각이 드실 때, 그것을 실행에 옮기는 방법을 생각해 보시거나 어떤 계획을 세우신 적이 있나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 환자 응답] 계획을 세운 적은 없어요. 근데 제가 그냥 안 깨어나면 가족이 더 나을지도 모른다는 생각이 계속 들어요. 그게 좀 무섭게 느껴져서 상사한테 얘기했어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="B38" s="5" t="inlineStr">
-        <is>
-          <t>[7번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="B39" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 의사 질문] 지난 2주 동안 이런 감정들과 기력 저하가 직장 업무나 일상적인 책임을 감당하는 데 어려움을 주었나요?</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" s="5" t="inlineStr">
-        <is>
-          <t>[8번째 턴 · 환자 응답] 네. 직장에서 실수를 하고 있는데, 상사가 새벽에 제가 트럭 안에 앉아 있는 걸 발견하고 산업보건팀까지 개입할 정도로 심각했어요. 집에서도 청구서나 다른 책임들을 평소처럼 처리하지 못하고 그냥 쌓아두고 있어요.</t>
-        </is>
-      </c>
-    </row>
-    <row r="41">
+배경 서술: 미겔이 그녀의 어머니와는 결혼한 적이 없지만 함께 키운 성인 딸이 조지아를 떠나 군에 입대하자, 그는 마치 그 변화가 자신이 더 큰 삶을 준비할 수 있음을 증명이라도 하는 듯 일과 집안 프로젝트에 몰두했다. 그는 대규모 창고 재설계를 밀어붙였고, 유난히 확신에 찬 태도로 지역 관리자가 될 거라고 이야기했으며, 외상으로 값비싼 빈티지 오토바이 부품을 사들였고, 계획과 아이디어로 머릿속이 넘쳐나는 상태를 유지했다. 그 후 2주 안에, 그 추진력 넘치던 시기는 우울한 시기로 바뀌어 그는 토마토 밭과 목공 작업대를 돌보지 않게 되었고, 팰컨스 경기나 교회 친교 모임에도 거의 관심을 두지 않았으며, 식욕을 잃었고, 움직임과 말이 느려졌으며, 딸을 떠나보낸 것이 자신의 잘못이라는 죄책감에 사로잡혔다. 물류센터에서의 집중력이 떨어져 배송 경로에서 실수를 저지르게 되었고 일상적인 인력 배치 문제조차 결정하지 못하게 되었으며, 개인적으로는 가족이 자기 없이 사는 게 더 나을 거라는 생각이 반복적으로 떠오르기 시작했다. 신뢰하던 교대 근무 관리자가 새벽녘에 그가 트럭 안에 혼자 앉아 있는 것을 발견했고 미겔이 죽음에 대한 생각을 인정한 뒤, 산업보건팀이 그를 직원 지원 프로그램 상담사와 연결해 주었고, 그는 정신건강의학과 평가에 의뢰되었다.
+표집된 증상 목록:
+  - S025 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - S026 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - S028 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.
+  - S030 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - S031 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.
+  - S032 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
+  - S033 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.
+  - S034 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.
+  - S035 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).
+  - S038 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.
+  - S040 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.
+  - S041 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
+        </is>
+      </c>
       <c r="B41" s="5" t="inlineStr">
         <is>
-          <t>[8번째 턴 · 의사의 감별진단] 고확률: 주요우울장애 (D013); 적응장애 (D020) | 중간확률: 조현정동장애 (우울형) (D007); 제2형 양극성장애 (D009); 지속성 우울장애 (D014); 정신병적 양상을 동반한 주요우울장애 (D015); 외상후 스트레스장애 (D018) | 저확률: 조현정동장애 (양극형) (D006); 제1형 양극성장애 (D008); 정신병적 양상을 동반한 제1형 양극성장애 (D010)</t>
-        </is>
-      </c>
-    </row>
-    <row r="43">
-      <c r="A43" s="2" t="inlineStr">
-        <is>
-          <t>최종 진단 및 진단 체크리스트</t>
-        </is>
-      </c>
-    </row>
-    <row r="44">
-      <c r="A44" s="6" t="inlineStr">
-        <is>
-          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.2)</t>
-        </is>
-      </c>
-    </row>
-    <row r="45">
-      <c r="A45" s="5" t="inlineStr">
-        <is>
-          <t>지속 기간 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="46">
-      <c r="A46" s="5" t="inlineStr">
-        <is>
-          <t>기능적 손상 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="47">
-      <c r="A47" s="5" t="inlineStr">
-        <is>
-          <t>추가 요건 — 점수: None</t>
-        </is>
-      </c>
-    </row>
-    <row r="48">
-      <c r="A48" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: hypomanic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
-  확인된 근거: (없음)
-  누락: 상승/과민한 기분: 비정상적이고 지속적으로 고양되거나 팽창되거나 과민한 기분이 뚜렷하게 나타나는 기간.; 활동 증가: 비정상적이고 지속적으로 증가한 목표지향적 활동이나 에너지.; 과장된 자존감: 과장된 자존감이나 과대성(단순한 자신감 과잉부터 망상적 수준까지 다양할 수 있음).; 수면 욕구 감소: 수면 욕구가 감소함(예: 단 3시간만 자도 개운함을 느낌).; 압박된 언어: 평소보다 말이 많아지거나 계속 말하려는 압박감을 느낌.; 사고의 질주: 사고의 비약이나 생각이 질주하는 듯한 주관적 경험.; 조증성 산만함: 중요하지 않거나 관련 없는 외부 자극에 지나치게 쉽게 주의가 쏠림.; 목표지향 활동 증가: 목표지향적 활동(직장, 학업, 사회, 성적 영역)의 증가 또는 목적 없는 정신운동 초조.; 위험 결과 초래 행동: 고통스러운 결과를 초래할 가능성이 높은 활동에 지나치게 몰두함.</t>
-        </is>
-      </c>
-    </row>
-    <row r="49">
-      <c r="A49" s="5" t="inlineStr">
-        <is>
-          <t>체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
-  확인된 근거: 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.; 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.; 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.; 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).; 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.
-  누락: 수면 장해: 수면의 양이나 질에 현저한 변화가 있는 상태.; 정신운동 변화: 관찰 가능한 정신운동 활동의 증가 또는 감소.; 피로: 휴식으로 호전되지 않는 지속적인 피로와 뚜렷한 에너지 저하.; 사고력 저하: 사고력이나 집중력 저하, 또는 우유부단함.</t>
+          <t>의사의 최종 진단: 주요우울장애 (D013, ICD: F32.2)
+지속 기간 요건: None
+기능적 손상 요건: None
+추가 요건: None
+체크리스트 그룹: hypomanic_episode (관계=must_include, 요구개수=5, 충족개수=0, 커버리지=0.0)
+확인된 근거:
+  (없음)
+체크리스트 그룹: depressive_episode (관계=must_include, 요구개수=5, 충족개수=5, 커버리지=1.0)
+확인된 근거:
+  - 우울한 기분: 슬프거나 공허하거나 절망적인 기분이 지속되는 상태.
+  - 흥미 상실: 이전에 즐기던 활동에 대한 흥미나 즐거움이 뚜렷하게 감소한 상태.
+  - 체중/식욕 변화: 식욕이나 체중의 현저한 증가 또는 감소.
+  - 무가치감/죄책감: 무가치감이나 과도하거나 부적절한 죄책감(망상적일 수도 있으며, 단순히 아픈 것에 대한 자책이 아님).
+  - 죽음/자살: 반복되는 죽음에 대한 생각, 반복되는 자살 사고, 또는 자살 시도.</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="4">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="A43:B43"/>
+    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D009_S002_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S002_P001__claude-sonnet-5_kor.xlsx
@@ -733,6 +733,11 @@
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
         <is>
+          <t>환자 증상 프로필</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
           <t>최종 진단 및 진단 체크리스트</t>
         </is>
       </c>
@@ -783,11 +788,10 @@
       </c>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="3">
     <mergeCell ref="A1:B1"/>
     <mergeCell ref="A3:B3"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="A40:B40"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/human_validation/judge/kor/judge_D009_S002_P001__claude-sonnet-5_kor.xlsx
+++ b/human_validation/judge/kor/judge_D009_S002_P001__claude-sonnet-5_kor.xlsx
@@ -458,6 +458,7 @@
         </is>
       </c>
     </row>
+    <row r="2"/>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
@@ -472,7 +473,7 @@
         </is>
       </c>
       <c r="B4" s="4" t="n">
-        <v>0.1604</v>
+        <v>0.3125</v>
       </c>
     </row>
     <row r="5">
@@ -482,7 +483,7 @@
         </is>
       </c>
       <c r="B5" s="4" t="n">
-        <v>0.9167</v>
+        <v>0.6667</v>
       </c>
     </row>
     <row r="6">
@@ -492,7 +493,7 @@
         </is>
       </c>
       <c r="B6" s="4" t="n">
-        <v>0.1644</v>
+        <v>0.4062</v>
       </c>
     </row>
     <row r="7">
@@ -502,7 +503,7 @@
         </is>
       </c>
       <c r="B7" s="4" t="n">
-        <v>0</v>
+        <v>0.7857</v>
       </c>
     </row>
     <row r="8">
@@ -555,6 +556,7 @@
         <v>0.5</v>
       </c>
     </row>
+    <row r="13"/>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
